--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-4.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-4.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D2E04E-2486-6D49-B11C-DDF8F715D1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,8 +19,42 @@
     <definedName name="MethodPointer1">1035676272</definedName>
     <definedName name="MethodPointer2">418</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,7 +365,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -536,21 +576,41 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -559,7 +619,6 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout/>
               <c:numFmt formatCode="General" sourceLinked="0"/>
             </c:trendlineLbl>
           </c:trendline>
@@ -570,40 +629,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.4</c:v>
+                  <c:v>0.13999999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8</c:v>
+                  <c:v>8.0000000000000016E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4</c:v>
+                  <c:v>4.0000000000000008E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2</c:v>
+                  <c:v>2.0000000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1</c:v>
+                  <c:v>1.0000000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.08</c:v>
+                  <c:v>8.0000000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.04</c:v>
+                  <c:v>4.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.02</c:v>
+                  <c:v>2E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01</c:v>
+                  <c:v>1E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -613,54 +672,67 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$U$20:$U$32</c:f>
+              <c:f>'板 1 - Sheet1'!$V$20:$V$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2.4239999999999999</c:v>
+                  <c:v>2.3479999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.101</c:v>
+                  <c:v>2.0249999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7130000000000001</c:v>
+                  <c:v>1.637</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4259999999999999</c:v>
+                  <c:v>1.3499999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96099999999999997</c:v>
+                  <c:v>0.88500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82499999999999996</c:v>
+                  <c:v>0.749</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.39100000000000001</c:v>
+                  <c:v>0.315</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.25650000000000001</c:v>
+                  <c:v>0.18049999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.192</c:v>
+                  <c:v>0.11600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.14849999999999999</c:v>
+                  <c:v>7.2499999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.123</c:v>
+                  <c:v>4.7E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.2500000000000004E-2</c:v>
+                  <c:v>6.5000000000000058E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.6000000000000012E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-68F4-1247-8F25-8F485A0F0B98}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="153246720"/>
         <c:axId val="153277184"/>
       </c:scatterChart>
@@ -669,8 +741,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="153277184"/>
         <c:crosses val="autoZero"/>
@@ -681,21 +756,27 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="153246720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -708,20 +789,26 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -740,7 +827,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -782,7 +869,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -814,9 +901,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -848,6 +953,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1023,60 +1146,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:U32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AH53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="V3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
+      <c r="V4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6">
+        <v>0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>45618</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="V7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3">
         <v>0.72585648148148152</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1096,8 +1242,12 @@
         <f>(R9+S9)/2</f>
         <v>3.2555000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9">
+        <f t="shared" ref="V9:V31" si="0">U9-0.076</f>
+        <v>3.1795</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1114,11 +1264,15 @@
         <v>3.4</v>
       </c>
       <c r="U10">
-        <f t="shared" ref="U10:U32" si="0">(R10+S10)/2</f>
+        <f t="shared" ref="U10:U32" si="1">(R10+S10)/2</f>
         <v>3.2134999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10">
+        <f t="shared" si="0"/>
+        <v>3.1374999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1135,11 +1289,15 @@
         <v>3.2</v>
       </c>
       <c r="U11">
+        <f t="shared" si="1"/>
+        <v>3.3330000000000002</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="0"/>
-        <v>3.3330000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
+        <v>3.2570000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="R12" s="11">
         <v>3.339</v>
       </c>
@@ -1150,11 +1308,15 @@
         <v>3</v>
       </c>
       <c r="U12">
+        <f t="shared" si="1"/>
+        <v>3.3944999999999999</v>
+      </c>
+      <c r="V12">
         <f t="shared" si="0"/>
-        <v>3.3944999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
+        <v>3.3184999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1169,11 +1331,15 @@
         <v>2.8</v>
       </c>
       <c r="U13">
+        <f t="shared" si="1"/>
+        <v>3.2275</v>
+      </c>
+      <c r="V13">
         <f t="shared" si="0"/>
-        <v>3.2275</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21">
+        <v>3.1515</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1190,11 +1356,15 @@
         <v>2.6</v>
       </c>
       <c r="U14">
+        <f t="shared" si="1"/>
+        <v>3.1684999999999999</v>
+      </c>
+      <c r="V14">
         <f t="shared" si="0"/>
-        <v>3.1684999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
+        <v>3.0924999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1208,11 +1378,15 @@
         <v>2.4</v>
       </c>
       <c r="U15">
+        <f t="shared" si="1"/>
+        <v>2.907</v>
+      </c>
+      <c r="V15">
         <f t="shared" si="0"/>
-        <v>2.907</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21">
+        <v>2.831</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1229,11 +1403,15 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="U16">
+        <f t="shared" si="1"/>
+        <v>2.7635000000000001</v>
+      </c>
+      <c r="V16">
         <f t="shared" si="0"/>
-        <v>2.7635000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21">
+        <v>2.6875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1247,11 +1425,15 @@
         <v>2</v>
       </c>
       <c r="U17">
+        <f t="shared" si="1"/>
+        <v>2.4504999999999999</v>
+      </c>
+      <c r="V17">
         <f t="shared" si="0"/>
-        <v>2.4504999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
+        <v>2.3744999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1265,11 +1447,15 @@
         <v>1.8</v>
       </c>
       <c r="U18">
+        <f t="shared" si="1"/>
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="V18">
         <f t="shared" si="0"/>
-        <v>2.8730000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
+        <v>2.7970000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1283,11 +1469,15 @@
         <v>1.6</v>
       </c>
       <c r="U19">
+        <f t="shared" si="1"/>
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="V19">
         <f t="shared" si="0"/>
-        <v>2.4750000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21">
+        <v>2.399</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="R20" s="16">
         <v>2.73</v>
       </c>
@@ -1295,14 +1485,18 @@
         <v>2.1179999999999999</v>
       </c>
       <c r="T20">
-        <v>1.4</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="U20">
+        <f t="shared" si="1"/>
+        <v>2.4239999999999999</v>
+      </c>
+      <c r="V20">
         <f t="shared" si="0"/>
-        <v>2.4239999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
+        <v>2.3479999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1314,14 +1508,18 @@
         <v>1.9490000000000001</v>
       </c>
       <c r="T21">
-        <v>1.2</v>
+        <v>0.12</v>
       </c>
       <c r="U21">
+        <f t="shared" si="1"/>
+        <v>2.101</v>
+      </c>
+      <c r="V21">
         <f t="shared" si="0"/>
-        <v>2.101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
+        <v>2.0249999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1335,14 +1533,18 @@
         <v>1.776</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U22">
+        <f t="shared" si="1"/>
+        <v>1.7130000000000001</v>
+      </c>
+      <c r="V22">
         <f t="shared" si="0"/>
-        <v>1.7130000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
+        <v>1.637</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="R23" s="20">
         <v>1.4159999999999999</v>
       </c>
@@ -1350,14 +1552,18 @@
         <v>1.4359999999999999</v>
       </c>
       <c r="T23">
-        <v>0.8</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="U23">
+        <f t="shared" si="1"/>
+        <v>1.4259999999999999</v>
+      </c>
+      <c r="V23">
         <f t="shared" si="0"/>
-        <v>1.4259999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
+        <v>1.3499999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -1402,14 +1608,18 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="T24">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="U24">
+        <f t="shared" si="1"/>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="V24">
         <f t="shared" si="0"/>
-        <v>0.96099999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1459,14 +1669,18 @@
         <v>0.82</v>
       </c>
       <c r="T25">
-        <v>0.4</v>
+        <v>4.0000000000000008E-2</v>
       </c>
       <c r="U25">
+        <f t="shared" si="1"/>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="V25">
         <f t="shared" si="0"/>
-        <v>0.82499999999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1516,14 +1730,18 @@
         <v>0.39400000000000002</v>
       </c>
       <c r="T26">
-        <v>0.2</v>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="U26">
+        <f t="shared" si="1"/>
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="V26">
         <f t="shared" si="0"/>
-        <v>0.39100000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1573,14 +1791,18 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="T27">
-        <v>0.1</v>
+        <v>1.0000000000000002E-2</v>
       </c>
       <c r="U27">
+        <f t="shared" si="1"/>
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="V27">
         <f t="shared" si="0"/>
-        <v>0.25650000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
+        <v>0.18049999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1630,14 +1852,18 @@
         <v>0.19400000000000001</v>
       </c>
       <c r="T28">
-        <v>0.08</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="U28">
+        <f t="shared" si="1"/>
+        <v>0.192</v>
+      </c>
+      <c r="V28">
         <f t="shared" si="0"/>
-        <v>0.192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
+        <v>0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1687,14 +1913,18 @@
         <v>0.15</v>
       </c>
       <c r="T29">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U29">
+        <f t="shared" si="1"/>
+        <v>0.14849999999999999</v>
+      </c>
+      <c r="V29">
         <f t="shared" si="0"/>
-        <v>0.14849999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21">
+        <v>7.2499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1744,14 +1974,18 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="T30">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="U30">
+        <f t="shared" si="1"/>
+        <v>0.123</v>
+      </c>
+      <c r="V30">
         <f t="shared" si="0"/>
-        <v>0.123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1801,14 +2035,18 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="T31">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="U31">
+        <f t="shared" si="1"/>
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="V31">
         <f t="shared" si="0"/>
-        <v>8.2500000000000004E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21">
+        <v>6.5000000000000058E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1861,11 +2099,469 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6000000000000012E-2</v>
       </c>
+      <c r="V32">
+        <f>U32-0.076</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="18:34">
+      <c r="R39" cm="1">
+        <f t="array" ref="R39:Y44">TRANSPOSE(C25:H32)</f>
+        <v>0.83</v>
+      </c>
+      <c r="S39">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="T39">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="U39">
+        <v>0.19</v>
+      </c>
+      <c r="V39">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="X39">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="Y39">
+        <v>8.3000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="18:34">
+      <c r="R40">
+        <v>0.82</v>
+      </c>
+      <c r="S40">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="T40">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="U40">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="X40">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="Y40">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="18:34">
+      <c r="R41">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="S41">
+        <v>3.1379999999999999</v>
+      </c>
+      <c r="T41">
+        <v>2.7130000000000001</v>
+      </c>
+      <c r="U41">
+        <v>2.73</v>
+      </c>
+      <c r="V41">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="W41">
+        <v>1.65</v>
+      </c>
+      <c r="X41">
+        <v>1.4159999999999999</v>
+      </c>
+      <c r="Y41">
+        <v>0.96699999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="18:34">
+      <c r="R42">
+        <v>2.3359999999999999</v>
+      </c>
+      <c r="S42">
+        <v>2.6080000000000001</v>
+      </c>
+      <c r="T42">
+        <v>2.2370000000000001</v>
+      </c>
+      <c r="U42">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="V42">
+        <v>1.9490000000000001</v>
+      </c>
+      <c r="W42">
+        <v>1.776</v>
+      </c>
+      <c r="X42">
+        <v>1.4359999999999999</v>
+      </c>
+      <c r="Y42">
+        <v>0.95499999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="18:34">
+      <c r="R43">
+        <v>3.2829999999999999</v>
+      </c>
+      <c r="S43">
+        <v>3.258</v>
+      </c>
+      <c r="T43">
+        <v>3.4209999999999998</v>
+      </c>
+      <c r="U43">
+        <v>3.339</v>
+      </c>
+      <c r="V43">
+        <v>3.05</v>
+      </c>
+      <c r="W43">
+        <v>2.8919999999999999</v>
+      </c>
+      <c r="X43">
+        <v>2.5910000000000002</v>
+      </c>
+      <c r="Y43">
+        <v>3.161</v>
+      </c>
+    </row>
+    <row r="44" spans="18:34">
+      <c r="R44">
+        <v>3.2280000000000002</v>
+      </c>
+      <c r="S44">
+        <v>3.169</v>
+      </c>
+      <c r="T44">
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="U44">
+        <v>3.45</v>
+      </c>
+      <c r="V44">
+        <v>3.4049999999999998</v>
+      </c>
+      <c r="W44">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="X44">
+        <v>3.2229999999999999</v>
+      </c>
+      <c r="Y44">
+        <v>2.3660000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="18:34">
+      <c r="R47">
+        <v>8</v>
+      </c>
+      <c r="S47">
+        <v>7</v>
+      </c>
+      <c r="T47">
+        <v>6</v>
+      </c>
+      <c r="U47">
+        <v>5</v>
+      </c>
+      <c r="V47">
+        <v>4</v>
+      </c>
+      <c r="W47">
+        <v>3</v>
+      </c>
+      <c r="X47">
+        <v>2</v>
+      </c>
+      <c r="Y47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="18:34">
+      <c r="R48">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="S48">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="T48">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="U48">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.19</v>
+      </c>
+      <c r="W48">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="X48">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="Y48">
+        <v>0.83</v>
+      </c>
+      <c r="AA48">
+        <v>3.161</v>
+      </c>
+      <c r="AB48">
+        <v>2.5910000000000002</v>
+      </c>
+      <c r="AC48">
+        <v>2.8919999999999999</v>
+      </c>
+      <c r="AD48">
+        <v>3.05</v>
+      </c>
+      <c r="AE48">
+        <v>3.339</v>
+      </c>
+      <c r="AF48">
+        <v>3.4209999999999998</v>
+      </c>
+      <c r="AG48">
+        <v>3.258</v>
+      </c>
+      <c r="AH48">
+        <v>3.2829999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="18:34">
+      <c r="R49">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="S49">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="T49">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="U49">
+        <v>0.15</v>
+      </c>
+      <c r="V49">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="X49">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="Y49">
+        <v>0.82</v>
+      </c>
+      <c r="AA49">
+        <v>2.3660000000000001</v>
+      </c>
+      <c r="AB49">
+        <v>3.2229999999999999</v>
+      </c>
+      <c r="AC49">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="AD49">
+        <v>3.4049999999999998</v>
+      </c>
+      <c r="AE49">
+        <v>3.45</v>
+      </c>
+      <c r="AF49">
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="AG49">
+        <v>3.169</v>
+      </c>
+      <c r="AH49">
+        <v>3.2280000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="18:34">
+      <c r="R50">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="S50">
+        <v>1.4159999999999999</v>
+      </c>
+      <c r="T50">
+        <v>1.65</v>
+      </c>
+      <c r="U50">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="V50">
+        <v>2.73</v>
+      </c>
+      <c r="W50">
+        <v>2.7130000000000001</v>
+      </c>
+      <c r="X50">
+        <v>3.1379999999999999</v>
+      </c>
+      <c r="Y50">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="AA50">
+        <f>(AA48+AA49)/2</f>
+        <v>2.7635000000000001</v>
+      </c>
+      <c r="AB50">
+        <f t="shared" ref="AB50:AH50" si="2">(AB48+AB49)/2</f>
+        <v>2.907</v>
+      </c>
+      <c r="AC50">
+        <f t="shared" si="2"/>
+        <v>3.1684999999999999</v>
+      </c>
+      <c r="AD50">
+        <f t="shared" si="2"/>
+        <v>3.2275</v>
+      </c>
+      <c r="AE50">
+        <f t="shared" si="2"/>
+        <v>3.3944999999999999</v>
+      </c>
+      <c r="AF50">
+        <f t="shared" si="2"/>
+        <v>3.3330000000000002</v>
+      </c>
+      <c r="AG50">
+        <f t="shared" si="2"/>
+        <v>3.2134999999999998</v>
+      </c>
+      <c r="AH50">
+        <f t="shared" si="2"/>
+        <v>3.2555000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="18:34">
+      <c r="R51">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="S51">
+        <v>1.4359999999999999</v>
+      </c>
+      <c r="T51">
+        <v>1.776</v>
+      </c>
+      <c r="U51">
+        <v>1.9490000000000001</v>
+      </c>
+      <c r="V51">
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="W51">
+        <v>2.2370000000000001</v>
+      </c>
+      <c r="X51">
+        <v>2.6080000000000001</v>
+      </c>
+      <c r="Y51">
+        <v>2.3359999999999999</v>
+      </c>
+      <c r="AA51">
+        <f>ABS(AA48-AA49)</f>
+        <v>0.79499999999999993</v>
+      </c>
+      <c r="AB51">
+        <f t="shared" ref="AB51:AH51" si="3">ABS(AB48-AB49)</f>
+        <v>0.63199999999999967</v>
+      </c>
+      <c r="AC51">
+        <f t="shared" si="3"/>
+        <v>0.55299999999999994</v>
+      </c>
+      <c r="AD51">
+        <f t="shared" si="3"/>
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="AE51">
+        <f t="shared" si="3"/>
+        <v>0.11100000000000021</v>
+      </c>
+      <c r="AF51">
+        <f t="shared" si="3"/>
+        <v>0.17599999999999971</v>
+      </c>
+      <c r="AG51">
+        <f t="shared" si="3"/>
+        <v>8.8999999999999968E-2</v>
+      </c>
+      <c r="AH51">
+        <f t="shared" si="3"/>
+        <v>5.4999999999999716E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="18:34">
+      <c r="R52">
+        <v>3.161</v>
+      </c>
+      <c r="S52">
+        <v>2.5910000000000002</v>
+      </c>
+      <c r="T52">
+        <v>2.8919999999999999</v>
+      </c>
+      <c r="U52">
+        <v>3.05</v>
+      </c>
+      <c r="V52">
+        <v>3.339</v>
+      </c>
+      <c r="W52">
+        <v>3.4209999999999998</v>
+      </c>
+      <c r="X52">
+        <v>3.258</v>
+      </c>
+      <c r="Y52">
+        <v>3.2829999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="18:34">
+      <c r="R53">
+        <v>2.3660000000000001</v>
+      </c>
+      <c r="S53">
+        <v>3.2229999999999999</v>
+      </c>
+      <c r="T53">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="U53">
+        <v>3.4049999999999998</v>
+      </c>
+      <c r="V53">
+        <v>3.45</v>
+      </c>
+      <c r="W53">
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="X53">
+        <v>3.169</v>
+      </c>
+      <c r="Y53">
+        <v>3.2280000000000002</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="R47:Y53">
+    <sortCondition descending="1" ref="R47:Y47"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
